--- a/artfynd/A 53127-2022 artfynd.xlsx
+++ b/artfynd/A 53127-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120506291</v>
+        <v>120507103</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552323</v>
+        <v>552401</v>
       </c>
       <c r="R2" t="n">
-        <v>6707189</v>
+        <v>6707128</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120507103</v>
+        <v>120506291</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +809,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552401</v>
+        <v>552323</v>
       </c>
       <c r="R3" t="n">
-        <v>6707128</v>
+        <v>6707189</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53127-2022 artfynd.xlsx
+++ b/artfynd/A 53127-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120507103</v>
+        <v>120506291</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552401</v>
+        <v>552323</v>
       </c>
       <c r="R2" t="n">
-        <v>6707128</v>
+        <v>6707189</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Persson, Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120506291</v>
+        <v>120507103</v>
       </c>
       <c r="B3" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,34 +799,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552323</v>
+        <v>552401</v>
       </c>
       <c r="R3" t="n">
-        <v>6707189</v>
+        <v>6707128</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53127-2022 artfynd.xlsx
+++ b/artfynd/A 53127-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Säters skogsarter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120506291</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
           <t>Säters skogsarter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507103</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>